--- a/docs/backtrader/futures/沪深300期货 [IF.CFE].xlsx
+++ b/docs/backtrader/futures/沪深300期货 [IF.CFE].xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2026PythonWorld\warrenluccie.github.io\docs\backtrader\futures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\warrenpyquant\examples\warrenluccie.github.io\docs\backtrader\futures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6605C659-FDE7-4961-AC3C-DB45E1F8790D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52601B88-B01D-48FC-A9C3-682F32F77A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="当前合约" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
   <si>
     <t>序号</t>
   </si>
@@ -395,16 +395,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,7 +747,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
     <col min="2" max="2" width="15.75" customWidth="1"/>
@@ -763,64 +763,64 @@
     <col min="12" max="14" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="6" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -841,17 +841,17 @@
       <c r="K2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -885,7 +885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -919,7 +919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -953,7 +953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -987,7 +987,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1033,16 +1033,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1052,7 +1052,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -1061,7 +1061,7 @@
     <col min="5" max="5" width="8.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1154,11 +1154,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.75" customWidth="1"/>
-    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="22.75" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="17.25" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
@@ -1174,7 +1174,7 @@
     <col min="17" max="17" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1278,59 +1278,6 @@
       </c>
       <c r="Q2" s="2" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P4" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
